--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135011039</v>
+        <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>58141</v>
+        <v>96899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Tasbygget, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512788</v>
+        <v>512810</v>
       </c>
       <c r="R2" t="n">
-        <v>6512223</v>
+        <v>6511982</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,66 +790,57 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011039</t>
+          <t>https://artportalen.se/Sighting/136341179</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135011037</v>
+        <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>93378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103023</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Tasbygget, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512788</v>
+        <v>512867</v>
       </c>
       <c r="R3" t="n">
-        <v>6512223</v>
+        <v>6512043</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +864,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Förra årets torkade</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,66 +910,57 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011037</t>
+          <t>https://artportalen.se/Sighting/136340550</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135011055</v>
+        <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>58629</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Bläcksvikebäcken, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512788</v>
+        <v>512864</v>
       </c>
       <c r="R4" t="n">
-        <v>6512223</v>
+        <v>6512072</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,22 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,84 +998,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011055</t>
+          <t>https://artportalen.se/Sighting/136348792</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135010092</v>
+        <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>5201</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Bläcksvikebäcken, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512780</v>
+        <v>512868</v>
       </c>
       <c r="R5" t="n">
-        <v>6512217</v>
+        <v>6512049</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,22 +1090,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,33 +1104,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135010092</t>
+          <t>https://artportalen.se/Sighting/136348807</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135010559</v>
+        <v>136340740</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>57175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1210,25 +1161,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Tasbygget, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512804</v>
+        <v>512853</v>
       </c>
       <c r="R6" t="n">
-        <v>6512212</v>
+        <v>6512020</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1255,22 +1205,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sandbad</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,16 +1251,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135010559</t>
+          <t>https://artportalen.se/Sighting/136340740</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135010561</v>
+        <v>136341595</v>
       </c>
       <c r="B7" t="n">
-        <v>98131</v>
+        <v>57175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,41 +1268,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Tasbygget, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512804</v>
+        <v>512671</v>
       </c>
       <c r="R7" t="n">
-        <v>6512212</v>
+        <v>6511995</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1371,22 +1334,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Sandbad</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,7 +1380,2210 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136341595</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136340025</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tasbygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512871</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6512092</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136341817</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tasbygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>512701</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6512060</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341817</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136340026</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tasbygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>512871</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6512092</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136340416</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tasbygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>512875</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6512055</v>
+      </c>
+      <c r="S11" t="n">
+        <v>17</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340416</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136341818</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tasbygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>512701</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6512060</v>
+      </c>
+      <c r="S12" t="n">
+        <v>13</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341818</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136340415</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tasbygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>512875</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6512055</v>
+      </c>
+      <c r="S13" t="n">
+        <v>17</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>För högt upp för att se säkert. På grövre gren på äldre död gran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340415</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135011039</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>512788</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6512223</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135011039</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136340197</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58149</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>512857</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6512136</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340197</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135011037</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>512788</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6512223</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135011037</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135011055</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58629</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>512788</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6512223</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135011055</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135010092</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>512780</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6512217</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135010092</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136341631</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tasbygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>512686</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6512054</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341631</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135010559</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>512804</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6512212</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135010559</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136340196</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>512857</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6512136</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340196</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136339655</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99231</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>512801</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6512188</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136339655</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136340198</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99231</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>512857</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6512136</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340198</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135010561</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98131</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>512804</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6512212</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135010561</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136339757</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98176</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>512857</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6512143</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136339757</t>
         </is>
       </c>
     </row>
@@ -1424,6 +3595,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136340740</v>
       </c>
       <c r="B6" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136341595</v>
       </c>
       <c r="B7" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136340197</v>
       </c>
       <c r="B15" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136340740</v>
       </c>
       <c r="B6" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136341595</v>
       </c>
       <c r="B7" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136340197</v>
       </c>
       <c r="B15" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27925-2026 artfynd.xlsx
+++ b/artfynd/A 27925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136341179</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136340550</v>
       </c>
       <c r="B3" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136348792</v>
       </c>
       <c r="B4" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136348807</v>
       </c>
       <c r="B5" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136339655</v>
       </c>
       <c r="B22" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136340198</v>
       </c>
       <c r="B23" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>136339757</v>
       </c>
       <c r="B25" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
